--- a/output/pdf_financials_xlsx/CONE.xlsx
+++ b/output/pdf_financials_xlsx/CONE.xlsx
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.163157</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.163157</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.168257</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.168257</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.168257</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.255457</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.255457</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.255457</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.365958</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.365958</v>
       </c>
     </row>
     <row r="93">
@@ -5215,10 +5215,10 @@
         <v>-0.113931</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.081668</v>
+        <v>0.074098</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.026216</v>
+        <v>-0.013047</v>
       </c>
     </row>
     <row r="119">
@@ -6848,7 +6848,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -7514,7 +7518,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -8402,7 +8410,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -10320,7 +10332,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -13178,7 +13194,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>2.163157</v>
       </c>
@@ -15526,7 +15546,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CONE.xlsx
+++ b/output/pdf_financials_xlsx/CONE.xlsx
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.274854</v>
+        <v>0.41946</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.544917</v>
+        <v>0.775023</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.244378</v>
+        <v>0.283453</v>
       </c>
     </row>
     <row r="11">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.274854</v>
+        <v>-0.41946</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.544917</v>
+        <v>-0.775023</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.244378</v>
+        <v>-0.283453</v>
       </c>
     </row>
     <row r="12">
@@ -2024,31 +2024,31 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000693</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.247793</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.003482</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006518</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000159</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.125399</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005159</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.010783</v>
       </c>
     </row>
     <row r="35">
@@ -2098,31 +2098,31 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000693</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.247793</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.003482</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.006518</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000159</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.125399</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005159</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.010783</v>
       </c>
     </row>
     <row r="37">
@@ -2542,31 +2542,31 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.000693</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.298293</v>
+        <v>0.0505</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.003482</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008518</v>
+        <v>0.002</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000159</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1304</v>
+        <v>0.005001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.052509</v>
+        <v>0.04735</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.010783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">

--- a/output/pdf_financials_xlsx/CONE.xlsx
+++ b/output/pdf_financials_xlsx/CONE.xlsx
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.018625</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -4562,34 +4562,34 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004259</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003664</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009972</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014957</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.012696</v>
+        <v>0.023613</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00653</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.010598</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.00695</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.001258</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.00667</v>
       </c>
     </row>
     <row r="102">
@@ -4747,34 +4747,34 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.037339</v>
+        <v>-0.041598</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.053912</v>
+        <v>0.050248</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.22771</v>
+        <v>0.217738</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.121303</v>
+        <v>0.106346</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.020169</v>
+        <v>-0.009252</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.113903</v>
+        <v>0.107373</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.285792</v>
+        <v>0.29639</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.033584</v>
+        <v>0.040534</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.243716</v>
+        <v>0.244974</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.250406</v>
+        <v>0.243736</v>
       </c>
     </row>
     <row r="107">
@@ -15224,7 +15224,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -17032,7 +17036,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E173" s="5" t="n">
         <v>-0.004259</v>
       </c>
@@ -18268,7 +18276,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
